--- a/data/metadata/diccionario_base_final.xlsx
+++ b/data/metadata/diccionario_base_final.xlsx
@@ -695,10 +695,10 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>87.68000000000001</v>
+        <v>93.25</v>
       </c>
       <c r="D6">
-        <v>6436</v>
+        <v>7029</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -709,10 +709,10 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>14.58</v>
+        <v>9.44</v>
       </c>
       <c r="D7">
-        <v>7804</v>
+        <v>9419</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>9873</v>
+        <v>11486</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -779,10 +779,10 @@
         <v>12</v>
       </c>
       <c r="C12">
-        <v>87.68000000000001</v>
+        <v>93.25</v>
       </c>
       <c r="D12">
-        <v>11246</v>
+        <v>13101</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -793,10 +793,10 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>88.75</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="D13">
-        <v>407</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -810,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -835,7 +835,7 @@
         <v>12</v>
       </c>
       <c r="C16">
-        <v>87.68000000000001</v>
+        <v>93.25</v>
       </c>
       <c r="D16">
         <v>34</v>
@@ -849,10 +849,10 @@
         <v>12</v>
       </c>
       <c r="C17">
-        <v>87.68000000000001</v>
+        <v>93.25</v>
       </c>
       <c r="D17">
-        <v>930</v>
+        <v>979</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -863,10 +863,10 @@
         <v>12</v>
       </c>
       <c r="C18">
-        <v>12.32</v>
+        <v>6.75</v>
       </c>
       <c r="D18">
-        <v>972</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -894,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>461934</v>
+        <v>1403147</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>154180</v>
+        <v>232001</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1014,10 +1014,10 @@
         <v>12</v>
       </c>
       <c r="C29">
-        <v>12.32</v>
+        <v>6.75</v>
       </c>
       <c r="D29">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1028,10 +1028,10 @@
         <v>12</v>
       </c>
       <c r="C30">
-        <v>87.68000000000001</v>
+        <v>93.25</v>
       </c>
       <c r="D30">
-        <v>513</v>
+        <v>568</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1042,10 +1042,10 @@
         <v>12</v>
       </c>
       <c r="C31">
-        <v>87.68000000000001</v>
+        <v>93.25</v>
       </c>
       <c r="D31">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1056,10 +1056,10 @@
         <v>12</v>
       </c>
       <c r="C32">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D32">
-        <v>1277</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>977</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>991</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>4305</v>
+        <v>4716</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>98.83</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="D37">
         <v>6</v>
@@ -1182,7 +1182,7 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>98.83</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -1196,10 +1196,10 @@
         <v>12</v>
       </c>
       <c r="C42">
-        <v>99.98999999999999</v>
+        <v>99.98</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1224,7 +1224,7 @@
         <v>12</v>
       </c>
       <c r="C44">
-        <v>98.83</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="D44">
         <v>8</v>
@@ -1238,10 +1238,10 @@
         <v>12</v>
       </c>
       <c r="C45">
-        <v>99.98999999999999</v>
+        <v>99.98</v>
       </c>
       <c r="D45">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1252,10 +1252,10 @@
         <v>12</v>
       </c>
       <c r="C46">
-        <v>99.98999999999999</v>
+        <v>99.98</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
       <c r="C47">
-        <v>98.83</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="D47">
         <v>6</v>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>362</v>
+        <v>377</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1297,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>371</v>
+        <v>395</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1333,7 +1333,7 @@
         <v>12</v>
       </c>
       <c r="C52">
-        <v>77.59999999999999</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -1347,7 +1347,7 @@
         <v>64</v>
       </c>
       <c r="C53">
-        <v>22.4</v>
+        <v>18.46</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1402,7 +1402,7 @@
         <v>9</v>
       </c>
       <c r="C58">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1413,7 +1413,7 @@
         <v>64</v>
       </c>
       <c r="C59">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1424,7 +1424,7 @@
         <v>64</v>
       </c>
       <c r="C60">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1435,7 +1435,7 @@
         <v>64</v>
       </c>
       <c r="C61">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1446,7 +1446,7 @@
         <v>9</v>
       </c>
       <c r="C62">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="63" spans="1:4">

--- a/data/metadata/diccionario_base_final.xlsx
+++ b/data/metadata/diccionario_base_final.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="86">
   <si>
     <t>nombre_variable</t>
   </si>
@@ -58,9 +58,6 @@
     <t>archivo_origen_saberpro</t>
   </si>
   <si>
-    <t>cole_cod_dane_establecimiento</t>
-  </si>
-  <si>
     <t>cole_cod_dane_establecimiento_saber11</t>
   </si>
   <si>
@@ -91,19 +88,16 @@
     <t>estu_cod_reside_depto_saberpro</t>
   </si>
   <si>
-    <t>estu_cod_reside_mcpio</t>
-  </si>
-  <si>
     <t>estu_cod_reside_mcpio_saber11</t>
   </si>
   <si>
     <t>estu_cod_reside_mcpio_saberpro</t>
   </si>
   <si>
-    <t>estu_consecutivo_saber11</t>
-  </si>
-  <si>
-    <t>estu_consecutivo_saberpro</t>
+    <t>estu_consecutivo</t>
+  </si>
+  <si>
+    <t>estu_consecutivo_sbpro</t>
   </si>
   <si>
     <t>estu_depto_reside_saber11</t>
@@ -112,13 +106,19 @@
     <t>estu_depto_reside_saberpro</t>
   </si>
   <si>
-    <t>estu_fechanacimiento</t>
+    <t>estu_fechanacimiento_saber11</t>
   </si>
   <si>
     <t>IDate</t>
   </si>
   <si>
-    <t>estu_genero</t>
+    <t>estu_fechanacimiento_saberpro</t>
+  </si>
+  <si>
+    <t>estu_genero_saber11</t>
+  </si>
+  <si>
+    <t>estu_genero_saberpro</t>
   </si>
   <si>
     <t>estu_inst_codmunicipio</t>
@@ -130,9 +130,6 @@
     <t>estu_inst_municipio</t>
   </si>
   <si>
-    <t>estu_mcpio_presentacion</t>
-  </si>
-  <si>
     <t>estu_mcpio_presentacion_saber11</t>
   </si>
   <si>
@@ -157,12 +154,15 @@
     <t>estu_tipocarreradeseada</t>
   </si>
   <si>
-    <t>estu_tipodocumento</t>
-  </si>
-  <si>
     <t>estu_tipodocumento_actual_sbpro</t>
   </si>
   <si>
+    <t>estu_tipodocumento_saber11</t>
+  </si>
+  <si>
+    <t>estu_tipodocumento_saberpro</t>
+  </si>
+  <si>
     <t>estu_tipodocumentosb11_motivo_na</t>
   </si>
   <si>
@@ -172,7 +172,10 @@
     <t>estu_trabaja_actualmente_saberpro</t>
   </si>
   <si>
-    <t>fami_estratovivienda</t>
+    <t>fami_estratovivienda_saber11</t>
+  </si>
+  <si>
+    <t>fami_estratovivienda_saberpro</t>
   </si>
   <si>
     <t>fami_ingreso_familiar_mensual_saber11</t>
@@ -196,67 +199,70 @@
     <t>inst_origen</t>
   </si>
   <si>
-    <t>llave_reforzada_usada</t>
+    <t>percentil_global_motivo_na</t>
+  </si>
+  <si>
+    <t>percentil_global_saber11</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>percentil_global_saberpro</t>
+  </si>
+  <si>
+    <t>periodo_saber11</t>
+  </si>
+  <si>
+    <t>periodo_saberpro</t>
+  </si>
+  <si>
+    <t>periodo_sb11</t>
+  </si>
+  <si>
+    <t>periodo_sbpro</t>
+  </si>
+  <si>
+    <t>punt_c_naturales</t>
+  </si>
+  <si>
+    <t>punt_comuni_escrita</t>
+  </si>
+  <si>
+    <t>punt_global_saber11</t>
+  </si>
+  <si>
+    <t>punt_global_saberpro</t>
+  </si>
+  <si>
+    <t>punt_ingles_saber11</t>
+  </si>
+  <si>
+    <t>punt_ingles_saberpro</t>
+  </si>
+  <si>
+    <t>punt_lectura_critica_saber11</t>
+  </si>
+  <si>
+    <t>punt_lectura_critica_saberpro</t>
+  </si>
+  <si>
+    <t>punt_matematicas_saber11</t>
+  </si>
+  <si>
+    <t>punt_matematicas_saberpro</t>
+  </si>
+  <si>
+    <t>punt_sociales_ciudadanas_saber11</t>
+  </si>
+  <si>
+    <t>punt_sociales_ciudadanas_saberpro</t>
+  </si>
+  <si>
+    <t>puntaje_escala_comparable</t>
   </si>
   <si>
     <t>logical</t>
-  </si>
-  <si>
-    <t>percentil_global_motivo_na</t>
-  </si>
-  <si>
-    <t>percentil_global_saber11</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>percentil_global_saberpro</t>
-  </si>
-  <si>
-    <t>periodo_saber11</t>
-  </si>
-  <si>
-    <t>periodo_saberpro</t>
-  </si>
-  <si>
-    <t>punt_c_naturales</t>
-  </si>
-  <si>
-    <t>punt_comuni_escrita</t>
-  </si>
-  <si>
-    <t>punt_global_saber11</t>
-  </si>
-  <si>
-    <t>punt_global_saberpro</t>
-  </si>
-  <si>
-    <t>punt_ingles_saber11</t>
-  </si>
-  <si>
-    <t>punt_ingles_saberpro</t>
-  </si>
-  <si>
-    <t>punt_lectura_critica_saber11</t>
-  </si>
-  <si>
-    <t>punt_lectura_critica_saberpro</t>
-  </si>
-  <si>
-    <t>punt_matematicas_saber11</t>
-  </si>
-  <si>
-    <t>punt_matematicas_saberpro</t>
-  </si>
-  <si>
-    <t>punt_sociales_ciudadanas_saber11</t>
-  </si>
-  <si>
-    <t>punt_sociales_ciudadanas_saberpro</t>
-  </si>
-  <si>
-    <t>puntaje_escala_comparable</t>
   </si>
   <si>
     <t>rezago_anios</t>
@@ -608,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1">
@@ -670,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -684,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -695,10 +701,10 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>93.25</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>7029</v>
+        <v>10759</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -709,10 +715,10 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>9.44</v>
+        <v>54.61</v>
       </c>
       <c r="D7">
-        <v>9419</v>
+        <v>10513</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -723,10 +729,10 @@
         <v>12</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -740,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -754,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>12033</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -765,10 +771,10 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="D11">
-        <v>11486</v>
+        <v>16819</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -779,10 +785,10 @@
         <v>12</v>
       </c>
       <c r="C12">
-        <v>93.25</v>
+        <v>77.53</v>
       </c>
       <c r="D12">
-        <v>13101</v>
+        <v>454</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -793,10 +799,10 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>90.06999999999999</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>420</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -810,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>144</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -821,10 +827,10 @@
         <v>12</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>72.86</v>
       </c>
       <c r="D15">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -835,10 +841,10 @@
         <v>12</v>
       </c>
       <c r="C16">
-        <v>93.25</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>34</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -849,10 +855,10 @@
         <v>12</v>
       </c>
       <c r="C17">
-        <v>93.25</v>
+        <v>72.86</v>
       </c>
       <c r="D17">
-        <v>979</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -863,10 +869,10 @@
         <v>12</v>
       </c>
       <c r="C18">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1100</v>
+        <v>682324</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -877,10 +883,10 @@
         <v>12</v>
       </c>
       <c r="C19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>682324</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -894,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>1403147</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -905,10 +911,10 @@
         <v>12</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>20.52</v>
       </c>
       <c r="D21">
-        <v>232001</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -916,38 +922,35 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C22">
         <v>0</v>
-      </c>
-      <c r="D22">
-        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>12</v>
-      </c>
       <c r="C23">
         <v>0</v>
-      </c>
-      <c r="D23">
-        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C24">
         <v>0</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -961,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -975,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -989,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1003,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1014,10 +1017,10 @@
         <v>12</v>
       </c>
       <c r="C29">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>133</v>
+        <v>655</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1028,10 +1031,10 @@
         <v>12</v>
       </c>
       <c r="C30">
-        <v>93.25</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>568</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1042,10 +1045,10 @@
         <v>12</v>
       </c>
       <c r="C31">
-        <v>93.25</v>
+        <v>0.02</v>
       </c>
       <c r="D31">
-        <v>122</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1056,10 +1059,10 @@
         <v>12</v>
       </c>
       <c r="C32">
-        <v>0.04</v>
+        <v>20.63</v>
       </c>
       <c r="D32">
-        <v>1364</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1073,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1010</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1087,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1101,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>1168</v>
+        <v>5188</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1112,10 +1115,10 @@
         <v>12</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="D36">
-        <v>4716</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1126,10 +1129,10 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>98.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1143,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1154,10 +1157,10 @@
         <v>12</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>22.36</v>
       </c>
       <c r="D39">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1168,10 +1171,10 @@
         <v>12</v>
       </c>
       <c r="C40">
-        <v>100</v>
+        <v>77.64</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1182,7 +1185,7 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>98.70999999999999</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -1196,7 +1199,7 @@
         <v>12</v>
       </c>
       <c r="C42">
-        <v>99.98</v>
+        <v>99.45</v>
       </c>
       <c r="D42">
         <v>6</v>
@@ -1210,10 +1213,10 @@
         <v>12</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1224,7 +1227,7 @@
         <v>12</v>
       </c>
       <c r="C44">
-        <v>98.70999999999999</v>
+        <v>4.01</v>
       </c>
       <c r="D44">
         <v>8</v>
@@ -1238,10 +1241,10 @@
         <v>12</v>
       </c>
       <c r="C45">
-        <v>99.98</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="D45">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1252,10 +1255,10 @@
         <v>12</v>
       </c>
       <c r="C46">
-        <v>99.98</v>
+        <v>99.45</v>
       </c>
       <c r="D46">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1266,10 +1269,10 @@
         <v>12</v>
       </c>
       <c r="C47">
-        <v>98.70999999999999</v>
+        <v>99.45</v>
       </c>
       <c r="D47">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1280,10 +1283,10 @@
         <v>12</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="D48">
-        <v>377</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1297,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>395</v>
+        <v>408</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1311,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>7</v>
+        <v>449</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1319,21 +1322,24 @@
         <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="C51">
         <v>0</v>
+      </c>
+      <c r="D51">
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
       </c>
       <c r="C52">
-        <v>81.54000000000001</v>
+        <v>56.61</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -1341,32 +1347,32 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" t="s">
         <v>63</v>
       </c>
-      <c r="B53" t="s">
-        <v>64</v>
-      </c>
       <c r="C53">
-        <v>18.46</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
-        <v>0.05</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1374,10 +1380,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1385,98 +1391,104 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C57">
         <v>0</v>
+      </c>
+      <c r="D57">
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C58">
-        <v>0.06</v>
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C59">
-        <v>1.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="C60">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C61">
-        <v>0.25</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C62">
-        <v>0.02</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B64" t="s">
         <v>9</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -1484,7 +1496,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B66" t="s">
         <v>9</v>
@@ -1495,10 +1507,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -1506,7 +1518,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B68" t="s">
         <v>9</v>
@@ -1517,10 +1529,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B69" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -1528,7 +1540,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B70" t="s">
         <v>9</v>
@@ -1539,10 +1551,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" t="s">
         <v>82</v>
-      </c>
-      <c r="B71" t="s">
-        <v>61</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -1553,9 +1565,31 @@
         <v>83</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="C72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>84</v>
+      </c>
+      <c r="B73" t="s">
+        <v>82</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>85</v>
+      </c>
+      <c r="B74" t="s">
+        <v>82</v>
+      </c>
+      <c r="C74">
         <v>0</v>
       </c>
     </row>

--- a/data/metadata/diccionario_base_final.xlsx
+++ b/data/metadata/diccionario_base_final.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="83">
   <si>
     <t>nombre_variable</t>
   </si>
@@ -94,7 +94,7 @@
     <t>estu_cod_reside_mcpio_saberpro</t>
   </si>
   <si>
-    <t>estu_consecutivo</t>
+    <t>estu_consecutivo_sb11</t>
   </si>
   <si>
     <t>estu_consecutivo_sbpro</t>
@@ -154,9 +154,6 @@
     <t>estu_tipocarreradeseada</t>
   </si>
   <si>
-    <t>estu_tipodocumento_actual_sbpro</t>
-  </si>
-  <si>
     <t>estu_tipodocumento_saber11</t>
   </si>
   <si>
@@ -184,10 +181,10 @@
     <t>fami_ingreso_familiar_mensual_saberpro</t>
   </si>
   <si>
-    <t>fami_nivel_sisben</t>
-  </si>
-  <si>
-    <t>fami_nivelsisben</t>
+    <t>fami_nivelsisben_saber11</t>
+  </si>
+  <si>
+    <t>fami_nivelsisben_saberpro</t>
   </si>
   <si>
     <t>inst_cod_institucion</t>
@@ -215,12 +212,6 @@
   </si>
   <si>
     <t>periodo_saberpro</t>
-  </si>
-  <si>
-    <t>periodo_sb11</t>
-  </si>
-  <si>
-    <t>periodo_sbpro</t>
   </si>
   <si>
     <t>punt_c_naturales</t>
@@ -614,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1">
@@ -1132,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1146,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1157,10 +1148,10 @@
         <v>12</v>
       </c>
       <c r="C39">
-        <v>22.36</v>
+        <v>77.64</v>
       </c>
       <c r="D39">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1171,10 +1162,10 @@
         <v>12</v>
       </c>
       <c r="C40">
-        <v>77.64</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1185,10 +1176,10 @@
         <v>12</v>
       </c>
       <c r="C41">
-        <v>98.56999999999999</v>
+        <v>99.45</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1199,10 +1190,10 @@
         <v>12</v>
       </c>
       <c r="C42">
-        <v>99.45</v>
+        <v>1.76</v>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1213,10 +1204,10 @@
         <v>12</v>
       </c>
       <c r="C43">
-        <v>1.76</v>
+        <v>4.01</v>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1227,10 +1218,10 @@
         <v>12</v>
       </c>
       <c r="C44">
-        <v>4.01</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1241,7 +1232,7 @@
         <v>12</v>
       </c>
       <c r="C45">
-        <v>98.56999999999999</v>
+        <v>99.45</v>
       </c>
       <c r="D45">
         <v>9</v>
@@ -1255,10 +1246,10 @@
         <v>12</v>
       </c>
       <c r="C46">
-        <v>99.45</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="D46">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1283,10 +1274,10 @@
         <v>12</v>
       </c>
       <c r="C48">
-        <v>98.56999999999999</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>7</v>
+        <v>408</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1300,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>408</v>
+        <v>449</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1314,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>449</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1325,10 +1316,10 @@
         <v>12</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>56.61</v>
       </c>
       <c r="D51">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1336,24 +1327,21 @@
         <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C52">
-        <v>56.61</v>
-      </c>
-      <c r="D52">
-        <v>3</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" t="s">
         <v>62</v>
       </c>
-      <c r="B53" t="s">
-        <v>63</v>
-      </c>
       <c r="C53">
-        <v>43.39</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1361,10 +1349,10 @@
         <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54">
-        <v>0.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1372,7 +1360,7 @@
         <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1383,7 +1371,7 @@
         <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1394,13 +1382,10 @@
         <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57">
-        <v>22</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1408,13 +1393,10 @@
         <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>31</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1422,10 +1404,10 @@
         <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1433,10 +1415,10 @@
         <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="C60">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1444,10 +1426,10 @@
         <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="C61">
-        <v>1.43</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1455,10 +1437,10 @@
         <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C62">
-        <v>0.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1466,10 +1448,10 @@
         <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="C63">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1477,10 +1459,10 @@
         <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="C64">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1488,7 +1470,7 @@
         <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -1499,7 +1481,7 @@
         <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -1510,7 +1492,7 @@
         <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -1521,7 +1503,7 @@
         <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -1529,10 +1511,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B69" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -1540,10 +1522,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -1551,45 +1533,12 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B71" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
-        <v>83</v>
-      </c>
-      <c r="B72" t="s">
-        <v>9</v>
-      </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
-        <v>84</v>
-      </c>
-      <c r="B73" t="s">
-        <v>82</v>
-      </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
-        <v>85</v>
-      </c>
-      <c r="B74" t="s">
-        <v>82</v>
-      </c>
-      <c r="C74">
         <v>0</v>
       </c>
     </row>
